--- a/產生結果/20250622_測試2_台北-立人醫事檢驗所.xlsx
+++ b/產生結果/20250622_測試2_台北-立人醫事檢驗所.xlsx
@@ -1883,7 +1883,7 @@
       <c r="C9" s="119" t="n"/>
       <c r="D9" s="120" t="inlineStr">
         <is>
-          <t>台北 - 立人醫事檢驗所</t>
+          <t>立人醫事檢驗所</t>
         </is>
       </c>
       <c r="E9" s="121" t="n"/>
